--- a/Proyecto/Fase2/techcore-odoo/4_Inventario_Fisico_Odoo.xlsx
+++ b/Proyecto/Fase2/techcore-odoo/4_Inventario_Fisico_Odoo.xlsx
@@ -420,25 +420,25 @@
   <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>product_id/default_code</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>location_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>inventory_quantity</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Product/Internal Reference</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Counted Quantity</t>
         </is>
       </c>
     </row>
